--- a/05_Figures/F06_prediction/proteins/T2/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/d_1rm_ext/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -128,12 +128,21 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">LDHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXD</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACADS</t>
   </si>
   <si>
     <t xml:space="preserve">ACADSB</t>
   </si>
   <si>
+    <t xml:space="preserve">CCDC124</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLUH</t>
   </si>
   <si>
@@ -149,381 +158,351 @@
     <t xml:space="preserve">GSTZ1</t>
   </si>
   <si>
+    <t xml:space="preserve">MAVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELENBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLASP2</t>
+  </si>
+  <si>
     <t xml:space="preserve">IDI1</t>
   </si>
   <si>
-    <t xml:space="preserve">LDHD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXD</t>
+    <t xml:space="preserve">MT-ATP8</t>
   </si>
   <si>
     <t xml:space="preserve">NT5C3A</t>
   </si>
   <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLASP2</t>
+    <t xml:space="preserve">SUCLG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG2</t>
   </si>
   <si>
     <t xml:space="preserve">ECHDC3</t>
   </si>
   <si>
+    <t xml:space="preserve">FAM136A</t>
+  </si>
+  <si>
     <t xml:space="preserve">IVD</t>
   </si>
   <si>
-    <t xml:space="preserve">MT-ATP8</t>
+    <t xml:space="preserve">NIPSNAP3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSRB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDH13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETFDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSPT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDE</t>
   </si>
   <si>
     <t xml:space="preserve">NGLY1</t>
   </si>
   <si>
-    <t xml:space="preserve">SUCLG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIPSNAP3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDH13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSRB2</t>
-  </si>
-  <si>
     <t xml:space="preserve">PREB</t>
   </si>
   <si>
-    <t xml:space="preserve">MYOF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETFDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K3</t>
-  </si>
-  <si>
     <t xml:space="preserve">RNH1</t>
   </si>
   <si>
-    <t xml:space="preserve">CRYAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAM136A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDE</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIABLO</t>
   </si>
   <si>
     <t xml:space="preserve">FUS</t>
   </si>
   <si>
-    <t xml:space="preserve">GSPT1</t>
+    <t xml:space="preserve">PDAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7</t>
   </si>
   <si>
     <t xml:space="preserve">GSTM4</t>
   </si>
   <si>
-    <t xml:space="preserve">OPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7</t>
+    <t xml:space="preserve">MTAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTGES3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPNS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRKL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FGGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBA57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCA2</t>
   </si>
   <si>
     <t xml:space="preserve">MAP3K20</t>
   </si>
   <si>
-    <t xml:space="preserve">PTGES3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPNS1</t>
+    <t xml:space="preserve">MCCC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPDU1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OXSM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGPEP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCSD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTAN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRMT10C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADIRF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ART3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKMT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS7A</t>
   </si>
   <si>
     <t xml:space="preserve">COQ3</t>
   </si>
   <si>
-    <t xml:space="preserve">CPNE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRKL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FGGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT2</t>
+    <t xml:space="preserve">COQ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSRP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX3X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHODH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPHX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPRS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H6PD</t>
   </si>
   <si>
     <t xml:space="preserve">HIST2H2BE</t>
   </si>
   <si>
+    <t xml:space="preserve">HLA-B</t>
+  </si>
+  <si>
     <t xml:space="preserve">HNRNPK</t>
   </si>
   <si>
-    <t xml:space="preserve">IBA57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISCA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCCC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPDU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI</t>
+    <t xml:space="preserve">HSPA1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KCTD12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2HGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LACTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICU2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL1</t>
   </si>
   <si>
     <t xml:space="preserve">MRPS16</t>
   </si>
   <si>
-    <t xml:space="preserve">MTAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXSM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGPEP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCSD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMT10C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZYX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAD9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACOT13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADIRF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ART3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKMT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX3X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHODH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNPEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPHX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPRS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRHPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H6PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIGD1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILF3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCTD12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2HGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LACTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LETM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICU2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL1</t>
-  </si>
-  <si>
     <t xml:space="preserve">MTFP1</t>
   </si>
   <si>
@@ -536,6 +515,9 @@
     <t xml:space="preserve">MYL12B</t>
   </si>
   <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
     <t xml:space="preserve">NDUFB1</t>
   </si>
   <si>
@@ -591,6 +573,9 @@
   </si>
   <si>
     <t xml:space="preserve">PRKAR2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRPSAP1</t>
   </si>
   <si>
     <t xml:space="preserve">PSMD4</t>
@@ -1043,16 +1028,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.679529348542857</v>
+        <v>-0.911558999269337</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.16299599011282</v>
+        <v>-0.0947138861466384</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1076,29 +1061,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.679529348542857</v>
+        <v>-0.911558999269337</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.16299599011282</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.572139303482587</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.552238805970149</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.665936546164555</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.739758699489179</v>
-      </c>
+        <v>-0.0947138861466384</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1122,2206 +1099,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.575726486754586</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.905276913464029</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.96619599984074</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.25169466230158</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.670768734032882</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.32461194721595</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.55682467887345</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.73660728513138</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.213922230381698</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.238211667883725</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.872479500149687</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.441533153075539</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.231691542547862</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.546130877687415</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.825272835607113</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.566434368962202</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.719344379376174</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.448041721096852</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.773485241432305</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.427634401259071</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.129297375065806</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.42366880127157</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.543607963068909</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-2.0978927942513</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.552082571334159</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.539104175310091</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.14340358180042</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-1.05282689762196</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.719290416400625</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.10152927507537</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.944896868322447</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-4.34210103652749</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.671477490655361</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.510378305855798</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.569901684161741</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1.02105661029352</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.425131611967039</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.05238841370607</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.522435195139516</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.381359753393938</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.475953619878544</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.189478400850075</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.138564159233667</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.95611666273656</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.542256318926517</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.966457647566437</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0739674564584631</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.786023228043786</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.664445579132145</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.354315850776705</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.9571793683733</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.1436483938414</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.700497850588464</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.0861049132217</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.65313311557139</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.85616534181149</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-5.386088066898</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.153658653123234</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.12307552746548</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.738909226082023</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.227460710244341</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.263177296885279</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.1288494383575</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.34638111696949</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.821468728843226</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-2.20869154552439</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.02982618444333</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.206203629668827</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.143935699068402</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.536523551547395</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.399508957163343</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.140047362502235</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.139706182290039</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.718958331604324</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.384171286355107</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.00697165929641</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.572469413220553</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.970565986205107</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.44936153084781</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-1.18879174682388</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.3587691840865</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-2.33087718564522</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.161407756199122</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.737248974239275</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.317009872653571</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.0791160142234179</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.0340952914905519</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.298196918904658</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.778802907506379</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-3.00682071696148</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.00676462024527</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.0808116121978402</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.953308297950027</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.363412686806902</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.675365482160793</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.576110673306736</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.0808348931848744</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.692239227322522</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.300325264860803</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.413658202647008</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.916453036655304</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.249581446388219</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.0423071272354947</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.293237181738186</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.09691009474325</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.425154156628495</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0.25728968971992</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.744775230631814</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-1.1892592619052</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.547554146951877</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.8307662354717</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.34792687994177</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.50978189723366</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.311335286332708</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.59214225171278</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.244194478594075</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.443893980373592</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.712806038564294</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.38293230944716</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.51010229513423</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.924858438509891</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.0229828276372266</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.29301328185441</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.218319651059432</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.231618285062954</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.910381581561563</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.603780860611114</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0.147199450748989</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.42879927679404</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.0473492201374239</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.23055976569639</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.59972874454383</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.28388679807163</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.425308621089382</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-1.00799848422007</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.450301854780475</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.918308087198231</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.482729161319052</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0.067277012028956</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.38618764205499</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.268515873180498</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.900750272216737</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.227341206547193</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.286046572834456</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.17312600774729</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.970911018279511</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.96643688946655</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.13319388423025</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-1.92310567335943</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0.449554371561017</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.00700214089093998</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.0147750434158738</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.708988134339822</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-1.11327755012694</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-2.09058903725113</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.632342847969799</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0.091369185988858</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.193586693402408</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.69636656803875</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>0.236071014220477</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.410586888803763</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-2.47125010055872</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-1.11823412829795</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.832377268517358</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>0.452708534717067</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.609220957723117</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-1.3339400881175</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.518376217772521</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.265467113981526</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.359530272174046</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.584288860710129</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.469068043927671</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.64097096259054</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.213589287572794</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.39408433122385</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.744783976052094</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.191182469450917</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.548096366155195</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.551186221365123</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.0809905624652054</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.0953261658576063</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.624575751219083</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.254845078624514</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.376369621717084</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.43021794396756</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.695858509884822</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.336320762972681</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.592436822619238</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.0657660623808403</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-1.77705498054048</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.876546826045244</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>0.241383502600931</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0.0594898366850563</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.815638377961847</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.2029945844122</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.686986615412794</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.608764592675743</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.756678974951508</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.896280968157546</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.281357949948511</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3364,7 +1141,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>12.9280849865798</v>
+        <v>13.218873689304</v>
       </c>
     </row>
     <row r="3">
@@ -3381,7 +1158,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>8.12096463907235</v>
+        <v>8.31982454219014</v>
       </c>
     </row>
     <row r="4">
@@ -3398,7 +1175,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>9.51564916069008</v>
+        <v>9.49951132986618</v>
       </c>
     </row>
     <row r="5">
@@ -3415,7 +1192,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>13.093696241336</v>
+        <v>22.2152436050901</v>
       </c>
     </row>
     <row r="6">
@@ -3432,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8552781930243</v>
+        <v>15.2044205674625</v>
       </c>
     </row>
     <row r="7">
@@ -3449,7 +1226,7 @@
         <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>3.28622477395172</v>
+        <v>3.25250640130848</v>
       </c>
     </row>
     <row r="8">
@@ -3466,7 +1243,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>15.2234913695549</v>
+        <v>15.2208742447766</v>
       </c>
     </row>
     <row r="9">
@@ -3483,7 +1260,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>5.0403038374375</v>
+        <v>4.22752593289695</v>
       </c>
     </row>
     <row r="10">
@@ -3500,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>8.16362309111071</v>
+        <v>7.6987121303633</v>
       </c>
     </row>
     <row r="11">
@@ -3517,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>9.9684343688281</v>
+        <v>10.1549507819017</v>
       </c>
     </row>
     <row r="12">
@@ -3534,7 +1311,7 @@
         <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>15.926206133346</v>
+        <v>16.0556830084385</v>
       </c>
     </row>
     <row r="13">
@@ -3551,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9302178936579</v>
+        <v>9.34491938918443</v>
       </c>
     </row>
     <row r="14">
@@ -3568,7 +1345,7 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>9.60650678983765</v>
+        <v>9.57070318755742</v>
       </c>
     </row>
     <row r="15">
@@ -3585,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>7.84327911963452</v>
+        <v>7.6536156371551</v>
       </c>
     </row>
   </sheetData>
@@ -3661,10 +1438,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -3678,10 +1455,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -3695,10 +1472,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="7">
@@ -3712,10 +1489,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="8">
@@ -3729,10 +1506,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -3746,10 +1523,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="10">
@@ -3763,10 +1540,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="11">
@@ -3780,10 +1557,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -3797,10 +1574,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="13">
@@ -3814,10 +1591,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="14">
@@ -3831,10 +1608,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="15">
@@ -3848,10 +1625,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="16">
@@ -3865,10 +1642,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="17">
@@ -3882,10 +1659,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="18">
@@ -3899,10 +1676,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="19">
@@ -3916,10 +1693,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="20">
@@ -3933,10 +1710,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="21">
@@ -3950,10 +1727,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="22">
@@ -3967,10 +1744,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="23">
@@ -3984,10 +1761,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="24">
@@ -4001,10 +1778,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="25">
@@ -4018,10 +1795,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="26">
@@ -4035,10 +1812,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="27">
@@ -4052,10 +1829,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="28">
@@ -4069,10 +1846,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="29">
@@ -4086,10 +1863,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="30">
@@ -4103,10 +1880,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="31">
@@ -4120,10 +1897,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="32">
@@ -4137,10 +1914,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="33">
@@ -4154,10 +1931,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="34">
@@ -4171,10 +1948,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -4188,10 +1965,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -4205,10 +1982,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37">
@@ -4222,10 +1999,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="38">
@@ -4239,10 +2016,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="39">
@@ -4256,10 +2033,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="40">
@@ -4273,10 +2050,10 @@
         <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="41">
@@ -4341,10 +2118,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="45">
@@ -4409,10 +2186,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="49">
@@ -4426,10 +2203,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="50">
@@ -4494,10 +2271,10 @@
         <v>88</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="54">
@@ -4511,10 +2288,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="55">
@@ -4953,10 +2730,10 @@
         <v>115</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="81">
@@ -4970,10 +2747,10 @@
         <v>116</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="82">
@@ -4987,10 +2764,10 @@
         <v>117</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="83">
@@ -6537,91 +4314,6 @@
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="s">
-        <v>209</v>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="s">
-        <v>210</v>
-      </c>
-      <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="s">
-        <v>211</v>
-      </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="s">
-        <v>212</v>
-      </c>
-      <c r="D177" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="s">
-        <v>213</v>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T2/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/d_1rm_ext/spls/c_data/results.xlsx
@@ -1064,7 +1064,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.911558999269337</v>
@@ -1072,10 +1072,18 @@
       <c r="I3" t="n">
         <v>-0.0947138861466384</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.691542288557214</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.45771144278607</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.646062304614939</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.61203412802486</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1099,6 +1107,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.878535659837882</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.900810454506955</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.05011910179683</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.05909164536665</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.643638324556791</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.28336240766504</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.4690368445947</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.65811124004452</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0597518182078645</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.48395586141462</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.980388730163665</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.540262361275249</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0937057933022177</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.429713905010517</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.884843736268693</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.743203192431999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.717131555802452</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.252220128044861</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.818890422880757</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.400879559822909</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.120541326842853</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.40436499935466</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.2346410758245</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-2.04631238025557</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.307565685142507</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.594891447471601</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.985479764920926</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.02254334395436</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.672858739135812</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.18488500644927</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.895558171409724</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-2.85403763238768</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.820212311669001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.252988775725276</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.598022716087554</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.954284927746867</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.423051351057492</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.83522977120716</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.663323669161863</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.306264765384847</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.526754353352663</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.0545324389769182</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.133237265280855</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.989517794588591</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.29230864322008</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.03802791831432</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.160167160548816</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.827124495642003</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.419659538508277</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.40740876972256</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.83511677745608</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.143256721468645</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.727283292597025</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.22191464062365</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.952239906469973</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.961390318399573</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-2.17231617336</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.139030084634028</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.947869316380772</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.691569631912367</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.159180409220987</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.362067761311975</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.34105645707306</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.19200829159037</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.851520293499702</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-2.26345174359489</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.215116695499019</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.231834553215078</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.282384405701985</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.78519185490932</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.349380994189348</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.0965408403757257</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.102289877575283</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.75002838922482</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.368786566136234</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.13414452906688</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.474530226590398</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.933119597958477</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.66000219723828</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.23093674904467</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.15954728467112</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-2.32902456718626</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.269955310741929</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.728083081945957</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.243178154039909</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.16039882027293</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.11590032734748</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.256881876897208</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.585485638974474</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-2.43720467315409</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.07709086219664</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.130798969907276</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.20436469401421</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.543218207526945</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.687733451274539</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.55492305276269</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.0741833600509372</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.667769363957876</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.319161358649833</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.432626700546476</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.16189948664835</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.325933812862761</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.285865131287132</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.252001657869575</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.00075946806461</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.421999019226746</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.307048122075565</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.750645993696034</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-1.20104145958013</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.504580477209029</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-2.03431624018912</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.351233309174386</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.316461881292668</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.342123189670033</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.72649917890599</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.403192719094409</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.365810019106838</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.16417815952673</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.47790941911066</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.16843150286201</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.23152154381157</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.131209828744449</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.14806828581118</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.243786784532481</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.244787448563958</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.895981966453295</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.479211122230432</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.156567467773487</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.6084671746846</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.0636671634081044</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.00864290726801564</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.705125902485538</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.269579431689697</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.404807314212722</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.979794348025393</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.582820036989146</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.851241698885006</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.385986556303034</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.0376536628628356</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.29578668472209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.195719277319077</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.961136241349785</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.00784237753625716</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.340163190647907</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.754475096854164</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.978918384020858</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.682951767385862</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.06123450580335</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.56268400453136</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.311282198556296</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.16366178674559</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.117505958491827</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.911604908928335</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.10706738467845</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.47047725663294</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.716092139482697</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.0912866091839589</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.328615457689469</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.31670489523804</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.154931728115292</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.368512579287577</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-2.59309072620417</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1.11855754277835</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.694138313284139</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.476510250722266</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.504540696132197</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.953801337460205</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.717582622671123</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.212205091021008</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.623484295458673</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.412866094297962</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.419420980171803</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.855739603588944</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.280641906067415</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.42844465202883</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.709082458629076</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.245185873595275</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.37486491553802</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1.27210184061169</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.0430496122179455</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.0913572088733503</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.657510285618366</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.218845253314325</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.150887774500725</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.427267636678585</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.936302719142912</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.283021143783064</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.746340127831401</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.585727986947141</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-1.77554677812379</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.878531492743636</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.237026122990924</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.17689686529007</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.930627068982226</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.32320747371274</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.802483204146115</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.602111057055127</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.791757989544298</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.978545505629629</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.327853523845377</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
